--- a/suppl/Supplementary_Tables_S1-S5.xlsx
+++ b/suppl/Supplementary_Tables_S1-S5.xlsx
@@ -21481,7 +21481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -21504,7 +21504,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -21527,7 +21527,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -21550,7 +21550,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -21573,7 +21573,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -21596,7 +21596,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -21619,7 +21619,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -21642,7 +21642,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -21665,7 +21665,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -21688,7 +21688,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -21711,7 +21711,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -21734,7 +21734,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -21757,7 +21757,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -21780,7 +21780,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -21803,7 +21803,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -21826,7 +21826,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -21849,7 +21849,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -21872,7 +21872,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -21895,7 +21895,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -21918,7 +21918,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -21941,7 +21941,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -21964,7 +21964,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -21987,7 +21987,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -22010,7 +22010,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -22033,7 +22033,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -22056,7 +22056,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -22079,7 +22079,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -22102,7 +22102,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -22125,7 +22125,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -22148,7 +22148,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -22171,7 +22171,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -22194,7 +22194,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -22217,7 +22217,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -22240,7 +22240,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -22263,7 +22263,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -22286,7 +22286,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -22309,7 +22309,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -22332,7 +22332,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -22355,7 +22355,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -22378,7 +22378,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -22401,7 +22401,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -22424,7 +22424,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -22447,7 +22447,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -22470,7 +22470,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -22493,7 +22493,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -22516,7 +22516,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -22539,7 +22539,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -22562,7 +22562,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -22585,7 +22585,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -22608,7 +22608,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -22631,7 +22631,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -22654,7 +22654,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -22677,7 +22677,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -22700,7 +22700,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -22723,7 +22723,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -22746,7 +22746,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -22769,7 +22769,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -22792,7 +22792,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -22815,7 +22815,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -22838,7 +22838,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -22861,7 +22861,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -22884,7 +22884,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -22907,7 +22907,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -22930,7 +22930,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -22953,7 +22953,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -22976,7 +22976,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -22999,7 +22999,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -23022,7 +23022,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -23045,7 +23045,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -23068,7 +23068,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -23091,7 +23091,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -23114,7 +23114,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -23137,7 +23137,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -23160,7 +23160,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -23183,7 +23183,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -23206,7 +23206,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -23229,7 +23229,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -23252,7 +23252,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -23275,7 +23275,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -23298,7 +23298,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -23321,7 +23321,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -23344,7 +23344,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -23367,7 +23367,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -23390,7 +23390,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -23413,7 +23413,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -23436,7 +23436,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -23459,7 +23459,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -23482,7 +23482,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -23505,7 +23505,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -23528,7 +23528,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -23551,7 +23551,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -23574,7 +23574,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -23597,7 +23597,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -23620,7 +23620,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -23643,7 +23643,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -23666,7 +23666,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -23689,7 +23689,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -23712,7 +23712,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -23735,7 +23735,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -23758,7 +23758,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -23781,7 +23781,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -23804,7 +23804,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -23827,7 +23827,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -23850,7 +23850,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -23873,7 +23873,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -23896,7 +23896,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -23919,7 +23919,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -23942,7 +23942,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -23965,7 +23965,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -23988,7 +23988,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -24011,7 +24011,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -24034,7 +24034,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -24057,7 +24057,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -24080,7 +24080,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -24103,7 +24103,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -24126,7 +24126,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -24149,7 +24149,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -24172,7 +24172,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -24195,7 +24195,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -24218,7 +24218,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -24241,7 +24241,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -24264,7 +24264,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -24287,7 +24287,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -24310,7 +24310,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -24333,7 +24333,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -24356,7 +24356,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -24379,7 +24379,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -24402,7 +24402,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -24425,7 +24425,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -24448,7 +24448,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -24471,7 +24471,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -24494,7 +24494,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -24517,7 +24517,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -24540,7 +24540,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
@@ -24563,7 +24563,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -24586,7 +24586,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -24609,7 +24609,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -24632,7 +24632,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -24655,7 +24655,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -24678,7 +24678,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -24701,7 +24701,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -24724,7 +24724,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -24747,7 +24747,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
@@ -24770,7 +24770,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
@@ -24793,7 +24793,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
@@ -24816,7 +24816,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
@@ -24839,7 +24839,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
@@ -24862,7 +24862,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
@@ -24885,7 +24885,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
@@ -24908,7 +24908,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
@@ -24931,7 +24931,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
@@ -24954,7 +24954,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
@@ -24977,7 +24977,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
@@ -25000,7 +25000,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
@@ -25023,7 +25023,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
@@ -25046,7 +25046,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -25069,7 +25069,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
@@ -25092,7 +25092,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
@@ -25115,7 +25115,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
@@ -25138,7 +25138,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
@@ -25161,7 +25161,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
@@ -25184,7 +25184,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -25207,7 +25207,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
@@ -25230,7 +25230,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
@@ -25253,7 +25253,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
@@ -25276,7 +25276,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -25299,7 +25299,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
@@ -25322,7 +25322,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
@@ -25345,7 +25345,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
@@ -25368,7 +25368,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
@@ -25391,7 +25391,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -25414,7 +25414,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -25437,7 +25437,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
@@ -25460,7 +25460,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
@@ -25483,7 +25483,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
@@ -25506,7 +25506,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -25529,7 +25529,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -25552,7 +25552,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -25575,7 +25575,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -25598,7 +25598,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -25621,7 +25621,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -25644,7 +25644,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -25667,7 +25667,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -25690,7 +25690,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -25713,7 +25713,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -25736,7 +25736,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -25759,7 +25759,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
@@ -25782,7 +25782,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>相代谢·5</t>
+          <t>metabolic·5</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
@@ -25805,7 +25805,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>相代谢·5</t>
+          <t>metabolic·5</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
@@ -25828,7 +25828,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>相代谢·5</t>
+          <t>metabolic·5</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -25851,7 +25851,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>相代谢·5</t>
+          <t>metabolic·5</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
@@ -25874,7 +25874,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>相代谢·5</t>
+          <t>metabolic·5</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
@@ -25897,7 +25897,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>潘氏细胞·4</t>
+          <t>Paneth-cell·4</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
@@ -25920,7 +25920,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>潘氏细胞·4</t>
+          <t>Paneth-cell·4</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
@@ -25943,7 +25943,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>潘氏细胞·4</t>
+          <t>Paneth-cell·4</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -25966,7 +25966,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>潘氏细胞·4</t>
+          <t>Paneth-cell·4</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
@@ -25989,7 +25989,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>黏液杯状·5</t>
+          <t>goblet·5</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
@@ -26012,7 +26012,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>黏液杯状·5</t>
+          <t>goblet·5</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
@@ -26035,7 +26035,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>黏液杯状·5</t>
+          <t>goblet·5</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
@@ -26058,7 +26058,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>黏液杯状·5</t>
+          <t>goblet·5</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -26081,7 +26081,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>黏液杯状·5</t>
+          <t>goblet·5</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
@@ -26104,7 +26104,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
@@ -26127,7 +26127,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
@@ -26150,7 +26150,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -26173,7 +26173,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -26196,7 +26196,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -26219,7 +26219,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -26242,7 +26242,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -26265,7 +26265,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -26288,7 +26288,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -26311,7 +26311,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -26334,7 +26334,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -26357,7 +26357,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -26380,7 +26380,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -26403,7 +26403,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -26426,7 +26426,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
@@ -26449,7 +26449,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
@@ -26472,7 +26472,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
@@ -26495,7 +26495,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
@@ -26518,7 +26518,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
@@ -26541,7 +26541,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
@@ -26564,7 +26564,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
@@ -26587,7 +26587,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
@@ -26610,7 +26610,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
@@ -26633,7 +26633,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
@@ -26656,7 +26656,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
@@ -26679,7 +26679,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
@@ -26702,7 +26702,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
@@ -26725,7 +26725,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
@@ -26748,7 +26748,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
@@ -26771,7 +26771,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
@@ -26794,7 +26794,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
@@ -26817,7 +26817,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
@@ -26840,7 +26840,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
@@ -26863,7 +26863,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
@@ -26886,7 +26886,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
@@ -26909,7 +26909,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
@@ -26932,7 +26932,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
@@ -26955,7 +26955,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
@@ -26978,7 +26978,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
@@ -27001,7 +27001,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
@@ -27024,7 +27024,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
@@ -27047,7 +27047,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
@@ -27070,7 +27070,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
@@ -27093,7 +27093,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
@@ -27116,7 +27116,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
@@ -27139,7 +27139,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
@@ -27162,7 +27162,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
@@ -27185,7 +27185,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
@@ -27208,7 +27208,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
@@ -27231,7 +27231,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
@@ -27254,7 +27254,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
@@ -27277,7 +27277,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
@@ -27300,7 +27300,7 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
@@ -27323,7 +27323,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
@@ -27346,7 +27346,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
@@ -27369,7 +27369,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
@@ -27392,7 +27392,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
@@ -27415,7 +27415,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
@@ -27438,7 +27438,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B261" s="2" t="n">
@@ -27461,7 +27461,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
@@ -27484,7 +27484,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B263" s="2" t="n">
@@ -27507,7 +27507,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
@@ -27530,7 +27530,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B265" s="2" t="n">
@@ -27553,7 +27553,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
@@ -27576,7 +27576,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B267" s="2" t="n">
@@ -27599,7 +27599,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
@@ -27622,7 +27622,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B269" s="2" t="n">
@@ -27645,7 +27645,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
@@ -27668,7 +27668,7 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B271" s="2" t="n">
@@ -27691,7 +27691,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
@@ -27714,7 +27714,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B273" s="2" t="n">
@@ -27737,7 +27737,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
@@ -27760,7 +27760,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B275" s="2" t="n">
@@ -27783,7 +27783,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
@@ -27806,7 +27806,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B277" s="2" t="n">
@@ -27829,7 +27829,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
@@ -27852,7 +27852,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B279" s="2" t="n">
@@ -27875,7 +27875,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
@@ -27898,7 +27898,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B281" s="2" t="n">
@@ -27921,7 +27921,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
@@ -27944,7 +27944,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B283" s="2" t="n">
@@ -27967,7 +27967,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
@@ -27990,7 +27990,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B285" s="2" t="n">
@@ -28013,7 +28013,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
@@ -28036,7 +28036,7 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B287" s="2" t="n">
@@ -28059,7 +28059,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
@@ -28082,7 +28082,7 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B289" s="2" t="n">
@@ -28105,7 +28105,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
@@ -28128,7 +28128,7 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B291" s="2" t="n">
@@ -28151,7 +28151,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
@@ -28174,7 +28174,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B293" s="2" t="n">
@@ -28197,7 +28197,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
@@ -28220,7 +28220,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B295" s="2" t="n">
@@ -28243,7 +28243,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
@@ -28266,7 +28266,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B297" s="2" t="n">
@@ -28289,7 +28289,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
@@ -28312,7 +28312,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B299" s="2" t="n">
@@ -28335,7 +28335,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
@@ -28358,7 +28358,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B301" s="2" t="n">
@@ -28381,7 +28381,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B302" s="2" t="n">
@@ -28404,7 +28404,7 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B303" s="2" t="n">
@@ -28427,7 +28427,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B304" s="2" t="n">
@@ -28450,7 +28450,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B305" s="2" t="n">
@@ -28473,7 +28473,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B306" s="2" t="n">
@@ -28496,7 +28496,7 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B307" s="2" t="n">
@@ -28519,7 +28519,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
@@ -28542,7 +28542,7 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B309" s="2" t="n">
@@ -28565,7 +28565,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
@@ -28588,7 +28588,7 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B311" s="2" t="n">
@@ -28611,7 +28611,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
@@ -28634,7 +28634,7 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B313" s="2" t="n">
@@ -28657,7 +28657,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B314" s="2" t="n">
@@ -28680,7 +28680,7 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B315" s="2" t="n">
@@ -28703,7 +28703,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B316" s="2" t="n">
@@ -28726,7 +28726,7 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B317" s="2" t="n">
@@ -28749,7 +28749,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B318" s="2" t="n">
@@ -28772,7 +28772,7 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B319" s="2" t="n">
@@ -28795,7 +28795,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B320" s="2" t="n">
@@ -28818,7 +28818,7 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B321" s="2" t="n">
@@ -28841,7 +28841,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B322" s="2" t="n">
@@ -28864,7 +28864,7 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B323" s="2" t="n">
@@ -28887,7 +28887,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B324" s="2" t="n">
@@ -28910,7 +28910,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B325" s="2" t="n">
@@ -28933,7 +28933,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B326" s="2" t="n">
@@ -28956,7 +28956,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B327" s="2" t="n">
@@ -28979,7 +28979,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B328" s="2" t="n">
@@ -29002,7 +29002,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B329" s="2" t="n">
@@ -29025,7 +29025,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B330" s="2" t="n">
@@ -29048,7 +29048,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B331" s="2" t="n">
@@ -29071,7 +29071,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B332" s="2" t="n">
@@ -29094,7 +29094,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B333" s="2" t="n">
@@ -29117,7 +29117,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B334" s="2" t="n">
@@ -29140,7 +29140,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B335" s="2" t="n">
@@ -29163,7 +29163,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B336" s="2" t="n">
@@ -29186,7 +29186,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B337" s="2" t="n">
@@ -29209,7 +29209,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B338" s="2" t="n">
@@ -29232,7 +29232,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B339" s="2" t="n">
@@ -29255,7 +29255,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B340" s="2" t="n">
@@ -29278,7 +29278,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B341" s="2" t="n">
@@ -29301,7 +29301,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B342" s="2" t="n">
@@ -29324,7 +29324,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B343" s="2" t="n">
@@ -29347,7 +29347,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B344" s="2" t="n">
@@ -29370,7 +29370,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B345" s="2" t="n">
@@ -29393,7 +29393,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B346" s="2" t="n">
@@ -29416,7 +29416,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B347" s="2" t="n">
@@ -29439,7 +29439,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B348" s="2" t="n">
@@ -29462,7 +29462,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B349" s="2" t="n">
@@ -29485,7 +29485,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B350" s="2" t="n">
@@ -29508,7 +29508,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B351" s="2" t="n">
@@ -29531,7 +29531,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B352" s="2" t="n">
@@ -29554,7 +29554,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B353" s="2" t="n">
@@ -29577,7 +29577,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B354" s="2" t="n">
@@ -29600,7 +29600,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B355" s="2" t="n">
@@ -29623,7 +29623,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B356" s="2" t="n">
@@ -29646,7 +29646,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B357" s="2" t="n">
@@ -29669,7 +29669,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B358" s="2" t="n">
@@ -29692,7 +29692,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B359" s="2" t="n">
@@ -29715,7 +29715,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B360" s="2" t="n">
@@ -29738,7 +29738,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B361" s="2" t="n">
@@ -29761,7 +29761,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B362" s="2" t="n">
@@ -29784,7 +29784,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B363" s="2" t="n">
@@ -29807,7 +29807,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B364" s="2" t="n">
@@ -29830,7 +29830,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B365" s="2" t="n">
@@ -29853,7 +29853,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B366" s="2" t="n">
@@ -29876,7 +29876,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B367" s="2" t="n">
@@ -29899,7 +29899,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B368" s="2" t="n">
@@ -29922,7 +29922,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B369" s="2" t="n">
@@ -29945,7 +29945,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B370" s="2" t="n">
@@ -29968,7 +29968,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B371" s="2" t="n">
@@ -29991,7 +29991,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B372" s="2" t="n">
@@ -30014,7 +30014,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B373" s="2" t="n">
@@ -30037,7 +30037,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B374" s="2" t="n">
@@ -30060,7 +30060,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B375" s="2" t="n">
@@ -30083,7 +30083,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B376" s="2" t="n">
@@ -30106,7 +30106,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B377" s="2" t="n">
@@ -30129,7 +30129,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B378" s="2" t="n">
@@ -30152,7 +30152,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B379" s="2" t="n">
@@ -30175,7 +30175,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B380" s="2" t="n">
@@ -30198,7 +30198,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B381" s="2" t="n">
@@ -30221,7 +30221,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B382" s="2" t="n">
@@ -30244,7 +30244,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B383" s="2" t="n">
@@ -30267,7 +30267,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B384" s="2" t="n">
@@ -30290,7 +30290,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B385" s="2" t="n">
@@ -30313,7 +30313,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B386" s="2" t="n">
@@ -30336,7 +30336,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B387" s="2" t="n">
@@ -30359,7 +30359,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B388" s="2" t="n">
@@ -30382,7 +30382,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B389" s="2" t="n">
@@ -30405,7 +30405,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B390" s="2" t="n">
@@ -30428,7 +30428,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B391" s="2" t="n">
@@ -30451,7 +30451,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B392" s="2" t="n">
@@ -30474,7 +30474,7 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B393" s="2" t="n">
@@ -30497,7 +30497,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B394" s="2" t="n">
@@ -30520,7 +30520,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B395" s="2" t="n">
@@ -30543,7 +30543,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B396" s="2" t="n">
@@ -30566,7 +30566,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B397" s="2" t="n">
@@ -30589,7 +30589,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B398" s="2" t="n">
@@ -30612,7 +30612,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B399" s="2" t="n">
@@ -30635,7 +30635,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B400" s="2" t="n">
@@ -30658,7 +30658,7 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B401" s="2" t="n">
@@ -30681,7 +30681,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B402" s="2" t="n">
@@ -30704,7 +30704,7 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B403" s="2" t="n">
@@ -30727,7 +30727,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B404" s="2" t="n">
@@ -30750,7 +30750,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B405" s="2" t="n">
@@ -30773,7 +30773,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B406" s="2" t="n">
@@ -30796,7 +30796,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B407" s="2" t="n">
@@ -30819,7 +30819,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B408" s="2" t="n">
@@ -30842,7 +30842,7 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B409" s="2" t="n">
@@ -30865,7 +30865,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B410" s="2" t="n">
@@ -30888,7 +30888,7 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B411" s="2" t="n">
@@ -30911,7 +30911,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Up-regulated component</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B412" s="2" t="n">
@@ -30934,7 +30934,7 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B413" s="2" t="n">
@@ -30957,7 +30957,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B414" s="2" t="n">
@@ -30980,7 +30980,7 @@
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B415" s="2" t="n">
@@ -31003,7 +31003,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B416" s="2" t="n">
@@ -31026,7 +31026,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B417" s="2" t="n">
@@ -31049,7 +31049,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B418" s="2" t="n">
@@ -31072,7 +31072,7 @@
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B419" s="2" t="n">
@@ -31095,7 +31095,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B420" s="2" t="n">
@@ -31118,7 +31118,7 @@
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B421" s="2" t="n">
@@ -31141,7 +31141,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B422" s="2" t="n">
@@ -31164,7 +31164,7 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B423" s="2" t="n">
@@ -31187,7 +31187,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B424" s="2" t="n">
@@ -31210,7 +31210,7 @@
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B425" s="2" t="n">
@@ -31233,7 +31233,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B426" s="2" t="n">
@@ -31256,7 +31256,7 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B427" s="2" t="n">
@@ -31279,7 +31279,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B428" s="2" t="n">
@@ -31302,7 +31302,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B429" s="2" t="n">
@@ -31325,7 +31325,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B430" s="2" t="n">
@@ -31348,7 +31348,7 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B431" s="2" t="n">
@@ -31371,7 +31371,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B432" s="2" t="n">
@@ -31394,7 +31394,7 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B433" s="2" t="n">
@@ -31417,7 +31417,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B434" s="2" t="n">
@@ -31440,7 +31440,7 @@
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B435" s="2" t="n">
@@ -31463,7 +31463,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B436" s="2" t="n">
@@ -31486,7 +31486,7 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B437" s="2" t="n">
@@ -31509,7 +31509,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B438" s="2" t="n">
@@ -31532,7 +31532,7 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B439" s="2" t="n">
@@ -31555,7 +31555,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B440" s="2" t="n">
@@ -31578,7 +31578,7 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B441" s="2" t="n">
@@ -31601,7 +31601,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B442" s="2" t="n">
@@ -31624,7 +31624,7 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B443" s="2" t="n">
@@ -31647,7 +31647,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B444" s="2" t="n">
@@ -31670,7 +31670,7 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B445" s="2" t="n">
@@ -31693,7 +31693,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B446" s="2" t="n">
@@ -31716,7 +31716,7 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B447" s="2" t="n">
@@ -31739,7 +31739,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B448" s="2" t="n">
@@ -31762,7 +31762,7 @@
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B449" s="2" t="n">
@@ -31785,7 +31785,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B450" s="2" t="n">
@@ -31808,7 +31808,7 @@
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B451" s="2" t="n">
@@ -31831,7 +31831,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B452" s="2" t="n">
@@ -31854,7 +31854,7 @@
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B453" s="2" t="n">
@@ -31877,7 +31877,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B454" s="2" t="n">
@@ -31900,7 +31900,7 @@
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B455" s="2" t="n">
@@ -31923,7 +31923,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B456" s="2" t="n">
@@ -31946,7 +31946,7 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B457" s="2" t="n">
@@ -31969,7 +31969,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B458" s="2" t="n">
@@ -31992,7 +31992,7 @@
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B459" s="2" t="n">
@@ -32015,7 +32015,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B460" s="2" t="n">
@@ -32038,7 +32038,7 @@
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B461" s="2" t="n">
@@ -32061,7 +32061,7 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B462" s="2" t="n">
@@ -32084,7 +32084,7 @@
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B463" s="2" t="n">
@@ -32107,7 +32107,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B464" s="2" t="n">
@@ -32130,7 +32130,7 @@
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B465" s="2" t="n">
@@ -32153,7 +32153,7 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B466" s="2" t="n">
@@ -32176,7 +32176,7 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B467" s="2" t="n">
@@ -32199,7 +32199,7 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B468" s="2" t="n">
@@ -32222,7 +32222,7 @@
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B469" s="2" t="n">
@@ -32245,7 +32245,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B470" s="2" t="n">
@@ -32268,7 +32268,7 @@
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B471" s="2" t="n">
@@ -32291,7 +32291,7 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B472" s="2" t="n">
@@ -32314,7 +32314,7 @@
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B473" s="2" t="n">
@@ -32337,7 +32337,7 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B474" s="2" t="n">
@@ -32360,7 +32360,7 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B475" s="2" t="n">
@@ -32383,7 +32383,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B476" s="2" t="n">
@@ -32406,7 +32406,7 @@
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B477" s="2" t="n">
@@ -32429,7 +32429,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B478" s="2" t="n">
@@ -32452,7 +32452,7 @@
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B479" s="2" t="n">
@@ -32475,7 +32475,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B480" s="2" t="n">
@@ -32498,7 +32498,7 @@
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B481" s="2" t="n">
@@ -32521,7 +32521,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B482" s="2" t="n">
@@ -32544,7 +32544,7 @@
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B483" s="2" t="n">
@@ -32567,7 +32567,7 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B484" s="2" t="n">
@@ -32590,7 +32590,7 @@
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B485" s="2" t="n">
@@ -32613,7 +32613,7 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B486" s="2" t="n">
@@ -32636,7 +32636,7 @@
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B487" s="2" t="n">
@@ -32659,7 +32659,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B488" s="2" t="n">
@@ -32682,7 +32682,7 @@
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B489" s="2" t="n">
@@ -32705,7 +32705,7 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B490" s="2" t="n">
@@ -32728,7 +32728,7 @@
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B491" s="2" t="n">
@@ -32751,7 +32751,7 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B492" s="2" t="n">
@@ -32774,7 +32774,7 @@
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B493" s="2" t="n">
@@ -32797,7 +32797,7 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B494" s="2" t="n">
@@ -32820,7 +32820,7 @@
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B495" s="2" t="n">
@@ -32843,7 +32843,7 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B496" s="2" t="n">
@@ -32866,7 +32866,7 @@
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B497" s="2" t="n">
@@ -32889,7 +32889,7 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B498" s="2" t="n">
@@ -32912,7 +32912,7 @@
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B499" s="2" t="n">
@@ -32935,7 +32935,7 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B500" s="2" t="n">
@@ -32958,7 +32958,7 @@
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B501" s="2" t="n">
@@ -32981,7 +32981,7 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B502" s="2" t="n">
@@ -33004,7 +33004,7 @@
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B503" s="2" t="n">
@@ -33027,7 +33027,7 @@
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B504" s="2" t="n">
@@ -33050,7 +33050,7 @@
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B505" s="2" t="n">
@@ -33073,7 +33073,7 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B506" s="2" t="n">
@@ -33096,7 +33096,7 @@
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B507" s="2" t="n">
@@ -33119,7 +33119,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B508" s="2" t="n">
@@ -33142,7 +33142,7 @@
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B509" s="2" t="n">
@@ -33165,7 +33165,7 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B510" s="2" t="n">
@@ -33188,7 +33188,7 @@
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B511" s="2" t="n">
@@ -33211,7 +33211,7 @@
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B512" s="2" t="n">
@@ -33234,7 +33234,7 @@
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B513" s="2" t="n">
@@ -33257,7 +33257,7 @@
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B514" s="2" t="n">
@@ -33280,7 +33280,7 @@
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>Down-regulated component</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B515" s="2" t="n">
@@ -74149,7 +74149,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上皮·分化/功能</t>
+          <t>epithelial-differentiation</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -74209,7 +74209,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>上皮·基线/结构</t>
+          <t>epithelial-structural</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -74269,7 +74269,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>上皮分化·核心8</t>
+          <t>enterocyte-differentiation·8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -74329,7 +74329,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>上调分量(210)</t>
+          <t>up-component·210</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -74389,7 +74389,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>下调分量(103)</t>
+          <t>down-component·103</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -74449,7 +74449,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>泛间质·6</t>
+          <t>stromal/activation·6</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -74509,7 +74509,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>潘氏细胞·4</t>
+          <t>Paneth-cell·4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -74565,7 +74565,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>相代谢·5</t>
+          <t>metabolic·5</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -74625,7 +74625,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>纯上皮基线·7</t>
+          <t>pure-epithelial-baseline·7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -74685,7 +74685,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>间质·基线</t>
+          <t>stromal-baseline</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -74745,7 +74745,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>间质·激活/CAF</t>
+          <t>stroma/activated-CAF</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -74805,7 +74805,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>髓系·激活</t>
+          <t>myeloid-activation</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -74865,7 +74865,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>黏液杯状·5</t>
+          <t>goblet·5</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -74991,7 +74991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全4基因(DEFA5/6+OLFM4+SPINK1)</t>
+          <t>all four genes (DEFA5/6 + OLFM4 + SPINK1)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -75015,7 +75015,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -75027,7 +75027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>全4基因(DEFA5/6+OLFM4+SPINK1)</t>
+          <t>all four genes (DEFA5/6 + OLFM4 + SPINK1)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -75051,7 +75051,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -75063,7 +75063,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>全4基因(DEFA5/6+OLFM4+SPINK1)</t>
+          <t>all four genes (DEFA5/6 + OLFM4 + SPINK1)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -75087,7 +75087,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -75099,7 +75099,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>全4基因(DEFA5/6+OLFM4+SPINK1)</t>
+          <t>all four genes (DEFA5/6 + OLFM4 + SPINK1)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -75123,7 +75123,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -75135,7 +75135,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>全4基因(DEFA5/6+OLFM4+SPINK1)</t>
+          <t>all four genes (DEFA5/6 + OLFM4 + SPINK1)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -75159,7 +75159,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -75171,7 +75171,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>全4基因(DEFA5/6+OLFM4+SPINK1)</t>
+          <t>all four genes (DEFA5/6 + OLFM4 + SPINK1)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -75195,7 +75195,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -75207,7 +75207,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>纯潘氏(DEFA5+DEFA6)</t>
+          <t>Paneth core only (DEFA5 + DEFA6)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -75231,7 +75231,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -75243,7 +75243,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>纯潘氏(DEFA5+DEFA6)</t>
+          <t>Paneth core only (DEFA5 + DEFA6)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -75267,7 +75267,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -75279,7 +75279,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>纯潘氏(DEFA5+DEFA6)</t>
+          <t>Paneth core only (DEFA5 + DEFA6)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -75303,7 +75303,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -75315,7 +75315,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>纯潘氏(DEFA5+DEFA6)</t>
+          <t>Paneth core only (DEFA5 + DEFA6)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -75339,7 +75339,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -75351,7 +75351,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>纯潘氏(DEFA5+DEFA6)</t>
+          <t>Paneth core only (DEFA5 + DEFA6)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -75375,7 +75375,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -75387,7 +75387,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>纯潘氏(DEFA5+DEFA6)</t>
+          <t>Paneth core only (DEFA5 + DEFA6)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -75411,7 +75411,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -75423,7 +75423,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>仅OLFM4(干细胞共享)</t>
+          <t>OLFM4 only (shared with stem cells)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -75447,7 +75447,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -75459,7 +75459,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>仅OLFM4(干细胞共享)</t>
+          <t>OLFM4 only (shared with stem cells)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -75483,7 +75483,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -75495,7 +75495,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>仅OLFM4(干细胞共享)</t>
+          <t>OLFM4 only (shared with stem cells)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -75519,7 +75519,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -75531,7 +75531,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>仅OLFM4(干细胞共享)</t>
+          <t>OLFM4 only (shared with stem cells)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -75555,7 +75555,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -75567,7 +75567,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>仅OLFM4(干细胞共享)</t>
+          <t>OLFM4 only (shared with stem cells)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -75591,7 +75591,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -75603,7 +75603,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>仅OLFM4(干细胞共享)</t>
+          <t>OLFM4 only (shared with stem cells)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -75627,7 +75627,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -75639,7 +75639,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>仅SPINK1</t>
+          <t>SPINK1 only</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -75663,7 +75663,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -75675,7 +75675,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>仅SPINK1</t>
+          <t>SPINK1 only</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -75699,7 +75699,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -75711,7 +75711,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>仅SPINK1</t>
+          <t>SPINK1 only</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -75735,7 +75735,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -75747,7 +75747,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>仅SPINK1</t>
+          <t>SPINK1 only</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -75771,7 +75771,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -75783,7 +75783,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>仅SPINK1</t>
+          <t>SPINK1 only</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -75807,7 +75807,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>D 单调降</t>
+          <t>D (monotone decrease)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -75819,7 +75819,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>仅SPINK1</t>
+          <t>SPINK1 only</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -75843,7 +75843,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>D 单调降</t>
+          <t>D (monotone decrease)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -75855,7 +75855,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>去OLFM4(DEFA5/6+SPINK1)</t>
+          <t>without OLFM4 (DEFA5/6 + SPINK1)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -75879,7 +75879,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -75891,7 +75891,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>去OLFM4(DEFA5/6+SPINK1)</t>
+          <t>without OLFM4 (DEFA5/6 + SPINK1)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -75915,7 +75915,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -75927,7 +75927,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>去OLFM4(DEFA5/6+SPINK1)</t>
+          <t>without OLFM4 (DEFA5/6 + SPINK1)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -75951,7 +75951,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -75963,7 +75963,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>去OLFM4(DEFA5/6+SPINK1)</t>
+          <t>without OLFM4 (DEFA5/6 + SPINK1)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -75987,7 +75987,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -75999,7 +75999,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>去OLFM4(DEFA5/6+SPINK1)</t>
+          <t>without OLFM4 (DEFA5/6 + SPINK1)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -76023,7 +76023,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -76035,7 +76035,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>去OLFM4(DEFA5/6+SPINK1)</t>
+          <t>without OLFM4 (DEFA5/6 + SPINK1)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -76059,7 +76059,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>P 腺瘤峰</t>
+          <t>P (adenoma peak)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
